--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10987,7 +10987,7 @@
         <v>11089</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -21742,7 +21742,7 @@
         <v>6450</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -38755,7 +38755,7 @@
         <v>17568</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -21742,7 +21742,7 @@
         <v>6450</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -35170,7 +35170,7 @@
         <v>7340</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -38755,7 +38755,7 @@
         <v>17568</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65">
@@ -42340,7 +42340,7 @@
         <v>1496</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -10984,10 +10984,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11089</v>
+        <v>11092</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -21739,10 +21739,10 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -35167,10 +35167,10 @@
         <v>0.2347842277297364</v>
       </c>
       <c r="J64" t="n">
-        <v>7340</v>
+        <v>7344</v>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -38752,10 +38752,10 @@
         <v>0.2473688460606713</v>
       </c>
       <c r="J64" t="n">
-        <v>17568</v>
+        <v>17574</v>
       </c>
       <c r="K64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -42337,10 +42337,10 @@
         <v>0.08732939498879609</v>
       </c>
       <c r="J64" t="n">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.01439493603309882</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -10984,7 +10984,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11092</v>
+        <v>11093</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>38548</v>
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04510296972976414</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -45922,10 +45922,10 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J64" t="n">
-        <v>3792</v>
+        <v>3793</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>38509</v>
@@ -7384,7 +7384,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>30019</v>
@@ -10969,7 +10969,7 @@
         <v>0.01439493603309882</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>50256</v>
@@ -14554,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -21724,7 +21724,7 @@
         <v>0.0002735132178235483</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -25309,7 +25309,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -28907,7 +28907,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -35152,7 +35152,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>58530</v>
@@ -38737,7 +38737,7 @@
         <v>0.05359894151339212</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>38548</v>
@@ -42322,7 +42322,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>49124</v>
@@ -45907,7 +45907,7 @@
         <v>0.04510296972976414</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>32739</v>
@@ -49492,7 +49492,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -53077,7 +53077,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -7399,7 +7399,7 @@
         <v>-0.1858117252205922</v>
       </c>
       <c r="J64" t="n">
-        <v>2667</v>
+        <v>2669</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -10984,7 +10984,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J64" t="n">
-        <v>11093</v>
+        <v>11094</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -21739,7 +21739,7 @@
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>6453</v>
+        <v>6452</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -42337,7 +42337,7 @@
         <v>0.08732939498879609</v>
       </c>
       <c r="J64" t="n">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -39431,13 +39431,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>242077</v>
+        <v>242352</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.04952439584832693</v>
+        <v>0.05071665785115367</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -39455,10 +39455,10 @@
         <v>0.1320353722884503</v>
       </c>
       <c r="J73" t="n">
-        <v>17576</v>
+        <v>17577</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -39474,7 +39474,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.04654717300693581</v>
+        <v>-0.04762906846240179</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -39443,7 +39443,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>38548</v>
+        <v>39864</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -39452,7 +39452,7 @@
         <v>7793</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1320353722884503</v>
+        <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
         <v>17577</v>
@@ -39489,7 +39489,7 @@
         <v>0</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>-0.5052976845557929</v>
+        <v>-0.51895839016304</v>
       </c>
       <c r="J74" t="n">
         <v>12026</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11367,13 +11367,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>159612</v>
+        <v>159607</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.01633916177425723</v>
+        <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -11410,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.1198907350324537</v>
+        <v>-0.1198631638963203</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11394,7 +11394,7 @@
         <v>11094</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -22260,7 +22260,7 @@
         <v>6452</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -39458,7 +39458,7 @@
         <v>17577</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -4147,7 +4147,7 @@
         <v>2.565813106173346e-05</v>
       </c>
       <c r="J73" t="n">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -11391,10 +11391,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J73" t="n">
-        <v>11094</v>
+        <v>11097</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.0004757713442919333</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -22257,10 +22257,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>6452</v>
+        <v>6454</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -39440,7 +39440,7 @@
         <v>0.05071665785115367</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -39455,10 +39455,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17577</v>
+        <v>17580</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46684,7 +46684,7 @@
         <v>0.04510296972976414</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53919,16 +53919,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7367</v>
+        <v>7101</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0</v>
+        <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53962,7 +53962,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.02823401656033664</v>
+        <v>0.008167863681171665</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4147,7 +4147,7 @@
         <v>2.565813106173346e-05</v>
       </c>
       <c r="J73" t="n">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -22233,13 +22233,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>84114</v>
+        <v>85979</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.0004757713442919333</v>
+        <v>0.02265861027190332</v>
       </c>
       <c r="E73" t="n">
         <v>1</v>
@@ -22276,7 +22276,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.04646075564115367</v>
+        <v>-0.06714430267856104</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>
@@ -39455,7 +39455,7 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17580</v>
+        <v>17581</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -46699,7 +46699,7 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J73" t="n">
-        <v>3793</v>
+        <v>3795</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -7769,7 +7769,7 @@
         <v>0.0002660193529079241</v>
       </c>
       <c r="J73" t="n">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.02265861027190332</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -35833,7 +35833,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7344</v>
+        <v>7346</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -39440,7 +39440,7 @@
         <v>0.05071665785115367</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -39455,7 +39455,7 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17581</v>
+        <v>17583</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46675,16 +46675,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>65668</v>
+        <v>65789</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.04510296972976414</v>
+        <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -46699,7 +46699,7 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J73" t="n">
-        <v>3795</v>
+        <v>3796</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -46718,7 +46718,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.239416458549065</v>
+        <v>-0.2408153338704039</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4147,7 +4147,7 @@
         <v>2.565813106173346e-05</v>
       </c>
       <c r="J73" t="n">
-        <v>2254</v>
+        <v>2260</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -35833,7 +35833,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7346</v>
+        <v>7347</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -39455,7 +39455,7 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17583</v>
+        <v>17584</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.02265861027190332</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -39440,7 +39440,7 @@
         <v>0.05071665785115367</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -39458,7 +39458,7 @@
         <v>17584</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -43080,7 +43080,7 @@
         <v>1496</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -46684,7 +46684,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11394,7 +11394,7 @@
         <v>11097</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11391,10 +11391,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J73" t="n">
-        <v>11097</v>
+        <v>10870</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74">
@@ -35833,7 +35833,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7347</v>
+        <v>7348</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -39455,10 +39455,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17584</v>
+        <v>17585</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -43077,10 +43077,10 @@
         <v>0.02453022130943012</v>
       </c>
       <c r="J73" t="n">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11391,10 +11391,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J73" t="n">
-        <v>10870</v>
+        <v>11097</v>
       </c>
       <c r="K73" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22233,16 +22233,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>85979</v>
+        <v>86078</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.02265861027190332</v>
+        <v>0.02383614434902586</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -22276,7 +22276,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.06714430267856104</v>
+        <v>-0.06821719835498037</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -35833,7 +35833,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7348</v>
+        <v>7349</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -39440,7 +39440,7 @@
         <v>0.05071665785115367</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46684,7 +46684,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11394,7 +11394,7 @@
         <v>11097</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -22260,7 +22260,7 @@
         <v>6454</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -39455,10 +39455,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17585</v>
+        <v>17557</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11391,10 +11391,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J73" t="n">
-        <v>11097</v>
+        <v>11106</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -22257,10 +22257,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>6454</v>
+        <v>6457</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -35833,10 +35833,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7349</v>
+        <v>7350</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -39431,13 +39431,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>242352</v>
+        <v>242419</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>0.05071665785115367</v>
+        <v>0.05100713623002419</v>
       </c>
       <c r="E73" t="n">
         <v>4</v>
@@ -39455,10 +39455,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17557</v>
+        <v>17589</v>
       </c>
       <c r="K73" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -39474,7 +39474,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>-0.04762906846240179</v>
+        <v>-0.04789228567067763</v>
       </c>
       <c r="E74" t="n">
         <v>5</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -39458,7 +39458,7 @@
         <v>17589</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11391,10 +11391,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J73" t="n">
-        <v>11106</v>
+        <v>11108</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -35833,10 +35833,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J73" t="n">
-        <v>7350</v>
+        <v>7351</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -39455,10 +39455,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J73" t="n">
-        <v>17589</v>
+        <v>17597</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11394,7 +11394,7 @@
         <v>11108</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -22260,7 +22260,7 @@
         <v>6457</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -35836,7 +35836,7 @@
         <v>7351</v>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -39458,7 +39458,7 @@
         <v>17597</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -7772,7 +7772,7 @@
         <v>2670</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -11394,7 +11394,7 @@
         <v>11108</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -35836,7 +35836,7 @@
         <v>7351</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74">
@@ -39458,7 +39458,7 @@
         <v>17597</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -11394,7 +11394,7 @@
         <v>11108</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -39440,7 +39440,7 @@
         <v>0.05100713623002419</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46684,7 +46684,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11394,7 +11394,7 @@
         <v>11108</v>
       </c>
       <c r="K73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -39440,7 +39440,7 @@
         <v>0.05100713623002419</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46684,7 +46684,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -7754,7 +7754,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -11376,7 +11376,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18620,7 +18620,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -22242,7 +22242,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -25864,7 +25864,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29499,7 +29499,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -32455,7 +32455,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -35818,7 +35818,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -39440,7 +39440,7 @@
         <v>0.05100713623002419</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -43062,7 +43062,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -46684,7 +46684,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -50306,7 +50306,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -53928,7 +53928,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -1416,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>38509</v>
@@ -4452,60 +4452,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36758</v>
+        <v>40656</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.0958776072412436</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>34480</v>
+        <v>38509</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.1153076409914302</v>
+        <v>2.565813106173346e-05</v>
       </c>
       <c r="J82" t="n">
-        <v>764</v>
+        <v>2260</v>
       </c>
       <c r="K82" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>37279</v>
+        <v>36758</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01417378529843843</v>
+        <v>-0.0958776072412436</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>34605</v>
+        <v>34480</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4514,13 +4514,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.003625290023201856</v>
+        <v>-0.1153303399615138</v>
       </c>
       <c r="J83" t="n">
-        <v>1882</v>
+        <v>764</v>
       </c>
       <c r="K83" t="n">
-        <v>207</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="84">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.01417378529843843</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.003625290023201856</v>
       </c>
       <c r="J84" t="n">
         <v>1882</v>
@@ -4563,20 +4563,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>37936</v>
+        <v>37279</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01762386330105421</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>34605</v>
@@ -4591,32 +4591,32 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2105</v>
+        <v>1882</v>
       </c>
       <c r="K85" t="n">
-        <v>13</v>
+        <v>207</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>39575</v>
+        <v>37936</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.04320434415858287</v>
+        <v>0.01762386330105421</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>38573</v>
+        <v>34605</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -4625,32 +4625,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.1146655107643404</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2150</v>
+        <v>2105</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>40656</v>
+        <v>39575</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02731522425773847</v>
+        <v>0.04320434415858287</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>38573</v>
@@ -4662,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.1146655107643404</v>
       </c>
       <c r="J87" t="n">
-        <v>2171</v>
+        <v>2150</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -4684,10 +4684,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.02731522425773847</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>38573</v>
@@ -4702,7 +4702,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2208</v>
+        <v>2171</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4711,7 +4711,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -4724,10 +4724,10 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>38974</v>
+        <v>38573</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4736,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01039587276073938</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>2238</v>
+        <v>2208</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4748,23 +4748,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>36758</v>
+        <v>40656</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.0958776072412436</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>34480</v>
+        <v>38974</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -4773,35 +4773,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.1153076409914302</v>
+        <v>0.01039587276073938</v>
       </c>
       <c r="J90" t="n">
-        <v>764</v>
+        <v>2238</v>
       </c>
       <c r="K90" t="n">
-        <v>1282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37279</v>
+        <v>36758</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01417378529843843</v>
+        <v>-0.0958776072412436</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>34605</v>
+        <v>34480</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4810,32 +4810,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.003625290023201856</v>
+        <v>-0.1153076409914302</v>
       </c>
       <c r="J91" t="n">
-        <v>1882</v>
+        <v>764</v>
       </c>
       <c r="K91" t="n">
-        <v>209</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37936</v>
+        <v>37279</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01762386330105421</v>
+        <v>0.01417378529843843</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>34605</v>
@@ -4847,35 +4847,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.003625290023201856</v>
       </c>
       <c r="J92" t="n">
-        <v>2119</v>
+        <v>1882</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>39575</v>
+        <v>37936</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.04320434415858287</v>
+        <v>0.01762386330105421</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>38573</v>
+        <v>34605</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -4884,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.1146655107643404</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2152</v>
+        <v>2119</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -4896,20 +4896,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>85323</v>
+        <v>39575</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>1.155982312065698</v>
+        <v>0.04320434415858287</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>38573</v>
@@ -4921,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.1146655107643404</v>
       </c>
       <c r="J94" t="n">
-        <v>2172</v>
+        <v>2152</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4933,20 +4933,20 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>40656</v>
+        <v>85323</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>-0.5235047994093035</v>
+        <v>1.155982312065698</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>38573</v>
@@ -4961,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2210</v>
+        <v>2172</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4970,7 +4970,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -4980,49 +4980,86 @@
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>0</v>
+        <v>-0.5235047994093035</v>
       </c>
       <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>38573</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2210</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>40656</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>38509</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>466</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.01042179763046691</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>2239</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>3898</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>4029</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>466</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>1475</v>
       </c>
     </row>
@@ -5038,7 +5075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7754,7 +7791,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>30019</v>
@@ -8074,60 +8111,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>33515</v>
+        <v>50245</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.3322241925521529</v>
+        <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>30019</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-1</v>
+        <v>0.0002660193529079241</v>
       </c>
       <c r="J82" t="n">
-        <v>1711</v>
+        <v>2670</v>
       </c>
       <c r="K82" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35259</v>
+        <v>33515</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.05203640161121886</v>
+        <v>-0.3329684545725943</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>5501</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -8136,13 +8173,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K83" t="n">
-        <v>640</v>
+        <v>600</v>
       </c>
     </row>
     <row r="84">
@@ -8158,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.05203640161121886</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -8185,20 +8222,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>35957</v>
+        <v>35259</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01979636404889532</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>5501</v>
@@ -8213,29 +8250,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2301</v>
+        <v>1709</v>
       </c>
       <c r="K85" t="n">
-        <v>96</v>
+        <v>640</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>36296</v>
+        <v>35957</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.009427927802653169</v>
+        <v>0.01979636404889532</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>5501</v>
@@ -8250,29 +8287,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>2433</v>
+        <v>2301</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>46665</v>
+        <v>36296</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.2856788626845934</v>
+        <v>0.009427927802653169</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>5501</v>
@@ -8287,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>2588</v>
+        <v>2433</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -8296,23 +8333,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>49210</v>
+        <v>46665</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05453766205935926</v>
+        <v>0.2856788626845934</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
-        <v>38694</v>
+        <v>5501</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -8321,10 +8358,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>6.03399381930558</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>2615</v>
+        <v>2588</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8333,23 +8370,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>50189</v>
+        <v>49210</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.01989433042064621</v>
+        <v>0.05453766205935926</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>30073</v>
+        <v>38694</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -8358,10 +8395,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>-0.2227994004238383</v>
+        <v>6.03399381930558</v>
       </c>
       <c r="J89" t="n">
-        <v>2650</v>
+        <v>2615</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -8370,23 +8407,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>33515</v>
+        <v>50189</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.3322241925521529</v>
+        <v>0.01989433042064621</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>30073</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -8395,35 +8432,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-1</v>
+        <v>-0.2227994004238383</v>
       </c>
       <c r="J90" t="n">
-        <v>1711</v>
+        <v>2650</v>
       </c>
       <c r="K90" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>35972</v>
+        <v>33515</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.07331045800387886</v>
+        <v>-0.3322241925521529</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>5501</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -8432,32 +8469,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J91" t="n">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K91" t="n">
-        <v>643</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>35957</v>
+        <v>35972</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.0004169909929945513</v>
+        <v>0.07331045800387886</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>5501</v>
@@ -8472,29 +8509,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>2423</v>
+        <v>1709</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>643</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36296</v>
+        <v>35957</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.009427927802653169</v>
+        <v>-0.0004169909929945513</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>5501</v>
@@ -8509,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>2434</v>
+        <v>2423</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8518,20 +8555,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>46506</v>
+        <v>36296</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.2812982146793035</v>
+        <v>0.009427927802653169</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>5501</v>
@@ -8546,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>2588</v>
+        <v>2434</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8555,23 +8592,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49210</v>
+        <v>46506</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05814303530727218</v>
+        <v>0.2812982146793035</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>48801</v>
+        <v>5501</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -8580,10 +8617,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>7.871296127976732</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>2621</v>
+        <v>2588</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8592,59 +8629,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>49210</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.05814303530727218</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>48801</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>7.871296127976732</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2621</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>50265</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.02143873196504776</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>30019</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>62</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>-0.3835986967480174</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>2651</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>16750</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>30019</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>940</v>
       </c>
     </row>
@@ -8660,7 +8734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11376,7 +11450,7 @@
         <v>0.01630732396877348</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>50256</v>
@@ -11696,60 +11770,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>140598</v>
+        <v>159607</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1047165426029814</v>
+        <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>13523</v>
+        <v>50256</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2151</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.7417451253747875</v>
+        <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>2307</v>
+        <v>11108</v>
       </c>
       <c r="K82" t="n">
-        <v>7498</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>142870</v>
+        <v>140598</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01615954707748332</v>
+        <v>-0.1190987863940805</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>22868</v>
+        <v>13523</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -11758,13 +11832,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.6910448864896842</v>
+        <v>-0.7419619516476806</v>
       </c>
       <c r="J83" t="n">
-        <v>2292</v>
+        <v>2307</v>
       </c>
       <c r="K83" t="n">
-        <v>7522</v>
+        <v>7498</v>
       </c>
     </row>
     <row r="84">
@@ -11780,7 +11854,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.01615954707748332</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -11795,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.6910448864896842</v>
       </c>
       <c r="J84" t="n">
         <v>2292</v>
@@ -11807,23 +11881,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>142871</v>
+        <v>142870</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>6.999370056694897e-06</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>23501</v>
+        <v>22868</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -11832,32 +11906,32 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.02768060171418576</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>9924</v>
+        <v>2292</v>
       </c>
       <c r="K85" t="n">
-        <v>7</v>
+        <v>7522</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>143471</v>
+        <v>142871</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.004199592639513967</v>
+        <v>6.999370056694897e-06</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>23501</v>
@@ -11869,32 +11943,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.02768060171418576</v>
       </c>
       <c r="J86" t="n">
-        <v>10061</v>
+        <v>9924</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>134243</v>
+        <v>143471</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.06431961859888061</v>
+        <v>0.004199592639513967</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>23501</v>
@@ -11909,32 +11983,32 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>10308</v>
+        <v>10061</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>134380</v>
+        <v>134243</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.001020537383699709</v>
+        <v>-0.06431961859888061</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
-        <v>52340</v>
+        <v>23501</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11943,10 +12017,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>1.227139270669333</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>10560</v>
+        <v>10308</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -11955,23 +12029,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>157043</v>
+        <v>134380</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.1686486084238726</v>
+        <v>0.001020537383699709</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>52363</v>
+        <v>52340</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11980,10 +12054,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0004394344669468857</v>
+        <v>1.227139270669333</v>
       </c>
       <c r="J89" t="n">
-        <v>10802</v>
+        <v>10560</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -11992,23 +12066,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>140598</v>
+        <v>157043</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1047165426029814</v>
+        <v>0.1686486084238726</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>13523</v>
+        <v>52363</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -12017,35 +12091,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.7417451253747875</v>
+        <v>0.0004394344669468857</v>
       </c>
       <c r="J90" t="n">
-        <v>2307</v>
+        <v>10802</v>
       </c>
       <c r="K90" t="n">
-        <v>7498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>142870</v>
+        <v>140598</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01615954707748332</v>
+        <v>-0.1047165426029814</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>22868</v>
+        <v>13523</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -12054,35 +12128,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.6910448864896842</v>
+        <v>-0.7417451253747875</v>
       </c>
       <c r="J91" t="n">
-        <v>2291</v>
+        <v>2307</v>
       </c>
       <c r="K91" t="n">
-        <v>7530</v>
+        <v>7498</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>143249</v>
+        <v>142870</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.002652761251487366</v>
+        <v>0.01615954707748332</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>23501</v>
+        <v>22868</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -12091,32 +12165,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.02768060171418576</v>
+        <v>0.6910448864896842</v>
       </c>
       <c r="J92" t="n">
-        <v>9937</v>
+        <v>2291</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>7530</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>143471</v>
+        <v>143249</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.001549749038387703</v>
+        <v>0.002652761251487366</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>23501</v>
@@ -12128,32 +12202,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.02768060171418576</v>
       </c>
       <c r="J93" t="n">
-        <v>10072</v>
+        <v>9937</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>134299</v>
+        <v>143471</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.06392929581587917</v>
+        <v>0.001549749038387703</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>23501</v>
@@ -12168,32 +12242,32 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>10317</v>
+        <v>10072</v>
       </c>
       <c r="K94" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>139155</v>
+        <v>134299</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.03615812478127164</v>
+        <v>-0.06392929581587917</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>52340</v>
+        <v>23501</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -12202,71 +12276,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>1.227139270669333</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>10574</v>
+        <v>10317</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>139155</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.03615812478127164</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>52340</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>1.227139270669333</v>
+      </c>
+      <c r="J96" t="n">
+        <v>10574</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>157043</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.1285473033667493</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>51794</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>690</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.002751241880015285</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>10824</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>16445</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>38271</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>690</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>8517</v>
       </c>
     </row>
@@ -12282,7 +12393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14998,7 +15109,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -15318,7 +15429,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -15331,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -15346,16 +15457,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>42</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -15368,7 +15479,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -15383,10 +15494,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -15429,7 +15540,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -15442,7 +15553,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -15466,7 +15577,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -15479,7 +15590,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -15494,16 +15605,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -15516,7 +15627,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -15540,7 +15651,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -15553,7 +15664,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -15568,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -15577,7 +15688,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -15590,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -15614,7 +15725,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -15627,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -15642,16 +15753,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>42</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -15664,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -15679,16 +15790,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>36</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -15701,31 +15812,31 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
+        <v>7</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>36</v>
+      </c>
+      <c r="K92" t="n">
         <v>4</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>40</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -15738,7 +15849,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -15753,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -15762,7 +15873,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -15775,7 +15886,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -15799,7 +15910,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -15812,7 +15923,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -15827,7 +15938,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -15836,7 +15947,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -15849,7 +15960,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -15871,24 +15982,61 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>42</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -15904,7 +16052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18620,7 +18768,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -18940,20 +19088,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>8532</v>
+        <v>9133</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.06580532136209351</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -18968,16 +19116,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -18987,10 +19135,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.06580532136209351</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -19005,10 +19153,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -19051,20 +19199,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>8603</v>
+        <v>8532</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.008321612751992499</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -19082,13 +19230,13 @@
         <v>428</v>
       </c>
       <c r="K85" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -19098,10 +19246,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.008321612751992499</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -19116,29 +19264,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>470</v>
+        <v>428</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>9133</v>
+        <v>8603</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.06160641636638382</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -19153,7 +19301,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -19162,7 +19310,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -19172,10 +19320,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.06160641636638382</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -19190,7 +19338,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -19199,7 +19347,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -19212,7 +19360,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -19227,7 +19375,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -19236,20 +19384,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8532</v>
+        <v>9133</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.06580532136209351</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -19264,16 +19412,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>431</v>
+        <v>482</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -19283,10 +19431,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.06580532136209351</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -19301,29 +19449,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K91" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>8603</v>
+        <v>8532</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.008321612751992499</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -19338,16 +19486,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>471</v>
+        <v>428</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -19357,10 +19505,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.008321612751992499</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -19375,7 +19523,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -19384,20 +19532,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9133</v>
+        <v>8603</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.06160641636638382</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -19412,7 +19560,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -19421,7 +19569,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -19431,10 +19579,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.06160641636638382</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -19449,7 +19597,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -19458,7 +19606,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -19471,46 +19619,83 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>479</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>9133</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>482</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>601</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>51</v>
       </c>
     </row>
@@ -19526,7 +19711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -22242,7 +22427,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>2232</v>
@@ -22562,44 +22747,44 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>80224</v>
+        <v>86078</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.04579299188809858</v>
+        <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>2232</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>34967</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>6458</v>
       </c>
       <c r="K82" t="n">
-        <v>5790</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -22609,10 +22794,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.06800808568972327</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -22624,13 +22809,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J83" t="n">
-        <v>5257</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>651</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="84">
@@ -22673,20 +22858,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>80214</v>
+        <v>80224</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.0001246509772636618</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -22701,29 +22886,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>5978</v>
+        <v>5257</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>651</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>80203</v>
+        <v>80214</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>-0.0001371331687735308</v>
+        <v>-0.0001246509772636618</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -22738,16 +22923,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>6052</v>
+        <v>5978</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -22757,10 +22942,10 @@
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001371331687735308</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -22775,7 +22960,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>6133</v>
+        <v>6052</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -22784,7 +22969,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -22797,7 +22982,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -22812,7 +22997,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>6221</v>
+        <v>6133</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -22821,20 +23006,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>84074</v>
+        <v>80203</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.04826502749273718</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -22849,7 +23034,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>6317</v>
+        <v>6221</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -22858,20 +23043,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>80224</v>
+        <v>84074</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.04579299188809858</v>
+        <v>0.04826502749273718</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -22886,16 +23071,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>6317</v>
       </c>
       <c r="K90" t="n">
-        <v>5790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -22905,10 +23090,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.04579299188809858</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -22923,29 +23108,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>5257</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>661</v>
+        <v>5790</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>80214</v>
+        <v>80224</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.0001246509772636618</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -22960,29 +23145,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>5986</v>
+        <v>5257</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>661</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>80203</v>
+        <v>80214</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>-0.0001371331687735308</v>
+        <v>-0.0001246509772636618</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -22997,7 +23182,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>6060</v>
+        <v>5986</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -23006,7 +23191,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -23016,10 +23201,10 @@
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0</v>
+        <v>-0.0001371331687735308</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -23034,29 +23219,29 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>6136</v>
+        <v>6060</v>
       </c>
       <c r="K94" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>222254</v>
+        <v>80203</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>1.771143224068925</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -23071,68 +23256,105 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>6227</v>
+        <v>6136</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>222254</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>1.771143224068925</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>6227</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>84074</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>-0.6217210938835747</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>19374</v>
       </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>6320</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>3850</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>19374</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>6320</v>
       </c>
     </row>
@@ -23148,7 +23370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -25864,7 +26086,7 @@
         <v>0.01324634242783709</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -26184,20 +26406,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>13384</v>
+        <v>15375</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1294959349593496</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -26212,29 +26434,29 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>573</v>
+        <v>850</v>
       </c>
       <c r="K82" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>13718</v>
+        <v>13384</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.02495517035265989</v>
+        <v>-0.1294959349593496</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -26249,10 +26471,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K83" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84">
@@ -26268,7 +26490,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.02495517035265989</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -26295,20 +26517,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>14592</v>
+        <v>13718</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.06371191135734072</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -26323,29 +26545,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>751</v>
+        <v>568</v>
       </c>
       <c r="K85" t="n">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>14647</v>
+        <v>14592</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.003769188596491228</v>
+        <v>0.06371191135734072</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -26360,29 +26582,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>775</v>
+        <v>751</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>14990</v>
+        <v>14647</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.02341776472997883</v>
+        <v>0.003769188596491228</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -26397,7 +26619,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -26406,7 +26628,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -26416,10 +26638,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.02341776472997883</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -26434,7 +26656,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>816</v>
+        <v>794</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -26443,20 +26665,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>15375</v>
+        <v>14990</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.0256837891927952</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -26471,7 +26693,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>836</v>
+        <v>816</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -26480,20 +26702,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>13384</v>
+        <v>15375</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1294959349593496</v>
+        <v>0.0256837891927952</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -26508,29 +26730,29 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>573</v>
+        <v>836</v>
       </c>
       <c r="K90" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>13718</v>
+        <v>13384</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.02495517035265989</v>
+        <v>-0.1294959349593496</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -26545,29 +26767,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="K91" t="n">
-        <v>171</v>
+        <v>117</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>14592</v>
+        <v>13718</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.06371191135734072</v>
+        <v>0.02495517035265989</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -26582,29 +26804,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>758</v>
+        <v>568</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>14647</v>
+        <v>14592</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.003769188596491228</v>
+        <v>0.06371191135734072</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -26619,7 +26841,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>775</v>
+        <v>758</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -26628,20 +26850,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>14990</v>
+        <v>14647</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.02341776472997883</v>
+        <v>0.003769188596491228</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -26656,7 +26878,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -26665,7 +26887,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -26675,10 +26897,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.02341776472997883</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -26693,7 +26915,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>816</v>
+        <v>795</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -26702,59 +26924,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>14990</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>816</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>15375</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.0256837891927952</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>838</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>1991</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>265</v>
       </c>
     </row>
@@ -26783,7 +27042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -29499,7 +29758,7 @@
         <v>1.246305418719212</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -29819,20 +30078,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1250</v>
+        <v>1824</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.3146929824561404</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -29847,16 +30106,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -29866,10 +30125,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>-0.3146929824561404</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -29884,10 +30143,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>30</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -29930,20 +30189,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1759</v>
+        <v>1250</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.4072</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -29958,16 +30217,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -29977,10 +30236,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.4072</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -29995,29 +30254,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>812</v>
+        <v>1759</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.5383740761796475</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -30032,7 +30291,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -30041,7 +30300,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -30051,10 +30310,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>-0.5383740761796475</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -30069,7 +30328,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -30078,20 +30337,20 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1824</v>
+        <v>812</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>1.246305418719212</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -30115,20 +30374,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1250</v>
+        <v>1824</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.3146929824561404</v>
+        <v>1.246305418719212</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -30143,16 +30402,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -30162,10 +30421,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.3146929824561404</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -30180,29 +30439,29 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>30</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1759</v>
+        <v>1250</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.4072</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -30217,16 +30476,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -30236,10 +30495,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.4072</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -30254,7 +30513,7 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -30263,20 +30522,20 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>812</v>
+        <v>1759</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.5383740761796475</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -30291,7 +30550,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -30300,7 +30559,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -30310,10 +30569,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>-0.5383740761796475</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -30328,7 +30587,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -30337,20 +30596,20 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1824</v>
+        <v>812</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>1.246305418719212</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -30372,24 +30631,61 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>1.246305418719212</v>
+      </c>
+      <c r="E97" t="n">
+        <v>9</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>38</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>574</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
     </row>
@@ -30405,7 +30701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K72"/>
+  <dimension ref="A1:K73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -32455,7 +32751,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -32664,7 +32960,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -32677,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -32701,7 +32997,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -32714,7 +33010,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -32738,7 +33034,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -32751,7 +33047,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -32775,7 +33071,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -32788,7 +33084,7 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -32812,7 +33108,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -32825,7 +33121,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -32849,7 +33145,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -32862,7 +33158,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -32886,7 +33182,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -32899,7 +33195,7 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -32923,7 +33219,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -32936,7 +33232,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -32960,7 +33256,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -32973,7 +33269,7 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -32997,7 +33293,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -33010,7 +33306,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -33034,59 +33330,96 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>15</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
         <v>9</v>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="4" t="n">
+      <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33102,7 +33435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -35818,7 +36151,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>58530</v>
@@ -36138,60 +36471,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>82765</v>
+        <v>87522</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.01215589879052476</v>
+        <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>58530</v>
+      </c>
+      <c r="G82" t="n">
+        <v>83</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1074</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.002300587741393787</v>
+      </c>
+      <c r="J82" t="n">
+        <v>7353</v>
+      </c>
+      <c r="K82" t="n">
         <v>10</v>
-      </c>
-      <c r="F82" t="n">
-        <v>3891</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>-0.9346599496221663</v>
-      </c>
-      <c r="J82" t="n">
-        <v>218</v>
-      </c>
-      <c r="K82" t="n">
-        <v>6696</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>83172</v>
+        <v>82765</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.004917537606476167</v>
+        <v>-0.05435204862777359</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>48894</v>
+        <v>3891</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -36200,13 +36533,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>11.56592135697764</v>
+        <v>-0.9348099251093203</v>
       </c>
       <c r="J83" t="n">
-        <v>4713</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>2118</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="84">
@@ -36222,7 +36555,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.004917537606476167</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -36237,7 +36570,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>11.56592135697764</v>
       </c>
       <c r="J84" t="n">
         <v>4713</v>
@@ -36249,23 +36582,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22012</v>
+        <v>83172</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>-0.7353436252585005</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>48650</v>
+        <v>48894</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -36274,35 +36607,35 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>-0.004990387368593283</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>6613</v>
+        <v>4713</v>
       </c>
       <c r="K85" t="n">
-        <v>312</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>85283</v>
+        <v>22012</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>2.874386698164638</v>
+        <v>-0.7353436252585005</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>48568</v>
+        <v>48650</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -36311,32 +36644,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>-0.001685508735868448</v>
+        <v>-0.004990387368593283</v>
       </c>
       <c r="J86" t="n">
-        <v>6986</v>
+        <v>6613</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>85336</v>
+        <v>85283</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.0006214603144823705</v>
+        <v>2.874386698164638</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>48568</v>
@@ -36348,10 +36681,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>-0.001685508735868448</v>
       </c>
       <c r="J87" t="n">
-        <v>7074</v>
+        <v>6986</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -36360,23 +36693,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>84442</v>
+        <v>85336</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.01047623511765257</v>
+        <v>0.0006214603144823705</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
-        <v>48765</v>
+        <v>48568</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -36385,10 +36718,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.004056168670729699</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>7177</v>
+        <v>7074</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -36397,23 +36730,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>82681</v>
+        <v>84442</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>-0.02085455105279363</v>
+        <v>-0.01047623511765257</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>59550</v>
+        <v>48765</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -36422,10 +36755,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.2211627191633344</v>
+        <v>0.004056168670729699</v>
       </c>
       <c r="J89" t="n">
-        <v>7290</v>
+        <v>7177</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -36434,23 +36767,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>82765</v>
+        <v>82681</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.001015952879137891</v>
+        <v>-0.02085455105279363</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>3891</v>
+        <v>59550</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -36459,35 +36792,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.9346599496221663</v>
+        <v>0.2211627191633344</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>7290</v>
       </c>
       <c r="K90" t="n">
-        <v>6696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>83172</v>
+        <v>82765</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.004917537606476167</v>
+        <v>0.001015952879137891</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>48894</v>
+        <v>3891</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -36496,35 +36829,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>11.56592135697764</v>
+        <v>-0.9346599496221663</v>
       </c>
       <c r="J91" t="n">
-        <v>4713</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>2124</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>22012</v>
+        <v>83172</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>-0.7353436252585005</v>
+        <v>0.004917537606476167</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>48650</v>
+        <v>48894</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -36533,35 +36866,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>-0.004990387368593283</v>
+        <v>11.56592135697764</v>
       </c>
       <c r="J92" t="n">
-        <v>7087</v>
+        <v>4713</v>
       </c>
       <c r="K92" t="n">
-        <v>111</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>85283</v>
+        <v>22012</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>2.874386698164638</v>
+        <v>-0.7353436252585005</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>48568</v>
+        <v>48650</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -36570,32 +36903,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>-0.001685508735868448</v>
+        <v>-0.004990387368593283</v>
       </c>
       <c r="J93" t="n">
-        <v>6991</v>
+        <v>7087</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>85323</v>
+        <v>85283</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.0004690266524395249</v>
+        <v>2.874386698164638</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>48568</v>
@@ -36607,35 +36940,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>-0.001685508735868448</v>
       </c>
       <c r="J94" t="n">
-        <v>7078</v>
+        <v>6991</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>84442</v>
+        <v>85323</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>-0.0103254690997738</v>
+        <v>0.0004690266524395249</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>48765</v>
+        <v>48568</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -36644,71 +36977,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.004056168670729699</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>7188</v>
+        <v>7078</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>84442</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.0103254690997738</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>48765</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.004056168670729699</v>
+      </c>
+      <c r="J96" t="n">
+        <v>7188</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>82681</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>-0.02085455105279363</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>58530</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G97" t="n">
         <v>83</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H97" t="n">
         <v>1074</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.2239721111452886</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>7295</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>-84</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>54639</v>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G98" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="H97" s="4" t="n">
+      <c r="H98" s="4" t="n">
         <v>1074</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>7295</v>
       </c>
     </row>
@@ -36724,7 +37094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -39440,7 +39810,7 @@
         <v>0.05100713623002419</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>39864</v>
@@ -39760,60 +40130,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>231321</v>
+        <v>242419</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.003152727304266373</v>
+        <v>0.05128060573995854</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>22925</v>
+        <v>39864</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>7793</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.4399794801641587</v>
+        <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>12026</v>
+        <v>17597</v>
       </c>
       <c r="K82" t="n">
-        <v>3645</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>232951</v>
+        <v>231321</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.007046485187250617</v>
+        <v>-0.04578023999768995</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>35473</v>
+        <v>22925</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -39822,13 +40192,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.547350054525627</v>
+        <v>-0.51895839016304</v>
       </c>
       <c r="J83" t="n">
-        <v>11797</v>
+        <v>12026</v>
       </c>
       <c r="K83" t="n">
-        <v>3934</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="84">
@@ -39844,7 +40214,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.007046485187250617</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -39859,7 +40229,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.547350054525627</v>
       </c>
       <c r="J84" t="n">
         <v>11797</v>
@@ -39871,20 +40241,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>234923</v>
+        <v>232951</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.008465299569437349</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>35473</v>
@@ -39899,32 +40269,32 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>16589</v>
+        <v>11797</v>
       </c>
       <c r="K85" t="n">
-        <v>501</v>
+        <v>3934</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>235858</v>
+        <v>234923</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.003980027498371807</v>
+        <v>0.008465299569437349</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
-        <v>36098</v>
+        <v>35473</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -39933,32 +40303,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.01761903419502157</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>16328</v>
+        <v>16589</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>501</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>222106</v>
+        <v>235858</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>-0.05830626902627852</v>
+        <v>0.003980027498371807</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>36098</v>
@@ -39970,10 +40340,10 @@
         <v>0</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>0.01761903419502157</v>
       </c>
       <c r="J87" t="n">
-        <v>16562</v>
+        <v>16328</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -39982,23 +40352,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>221971</v>
+        <v>222106</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>-0.0006078178887558193</v>
+        <v>-0.05830626902627852</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
-        <v>36875</v>
+        <v>36098</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -40007,10 +40377,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02152473821264336</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>16962</v>
+        <v>16562</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -40019,23 +40389,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>230207</v>
+        <v>221971</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.03710394601096539</v>
+        <v>-0.0006078178887558193</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>40936</v>
+        <v>36875</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -40044,10 +40414,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.110128813559322</v>
+        <v>0.02152473821264336</v>
       </c>
       <c r="J89" t="n">
-        <v>17366</v>
+        <v>16962</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -40056,23 +40426,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>231321</v>
+        <v>230207</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>0.004839123050124453</v>
+        <v>0.03710394601096539</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>22925</v>
+        <v>40936</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -40081,35 +40451,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.4399794801641587</v>
+        <v>0.110128813559322</v>
       </c>
       <c r="J90" t="n">
-        <v>12026</v>
+        <v>17366</v>
       </c>
       <c r="K90" t="n">
-        <v>3645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>233665</v>
+        <v>231321</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01013310507908923</v>
+        <v>0.004839123050124453</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>35473</v>
+        <v>22925</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -40118,32 +40488,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.547350054525627</v>
+        <v>-0.4399794801641587</v>
       </c>
       <c r="J91" t="n">
-        <v>11796</v>
+        <v>12026</v>
       </c>
       <c r="K91" t="n">
-        <v>3957</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>234923</v>
+        <v>233665</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.005383775918515824</v>
+        <v>0.01013310507908923</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>35473</v>
@@ -40155,35 +40525,35 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.547350054525627</v>
       </c>
       <c r="J92" t="n">
-        <v>15994</v>
+        <v>11796</v>
       </c>
       <c r="K92" t="n">
-        <v>242</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>235831</v>
+        <v>234923</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.003865096223017755</v>
+        <v>0.005383775918515824</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
-        <v>36098</v>
+        <v>35473</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -40192,32 +40562,32 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.01761903419502157</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>16353</v>
+        <v>15994</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>222052</v>
+        <v>235831</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>-0.05842743320428612</v>
+        <v>0.003865096223017755</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>36098</v>
@@ -40229,35 +40599,35 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0</v>
+        <v>0.01761903419502157</v>
       </c>
       <c r="J94" t="n">
-        <v>16593</v>
+        <v>16353</v>
       </c>
       <c r="K94" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>222263</v>
+        <v>222052</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.0009502278745519068</v>
+        <v>-0.05842743320428612</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>36875</v>
+        <v>36098</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -40266,71 +40636,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.02152473821264336</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>16996</v>
+        <v>16593</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>222263</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.0009502278745519068</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>36875</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.02152473821264336</v>
+      </c>
+      <c r="J96" t="n">
+        <v>16996</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>231985</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.043740973531357</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>36636</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>4728</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.121735593220339</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>17383</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K97" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>664</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>13711</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>4728</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>5357</v>
       </c>
     </row>
@@ -40346,7 +40753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -43062,7 +43469,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>49124</v>
@@ -43382,60 +43789,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21722</v>
+        <v>25642</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.1275604466222187</v>
+        <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>3183</v>
+        <v>49124</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>4253</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.9389047774429452</v>
+        <v>0.02453022130943012</v>
       </c>
       <c r="J82" t="n">
-        <v>958</v>
+        <v>1502</v>
       </c>
       <c r="K82" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>21735</v>
+        <v>21722</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.0005984715956173465</v>
+        <v>-0.1528741907807503</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>2490</v>
+        <v>3183</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -43444,13 +43851,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>-0.2177191328934967</v>
+        <v>-0.9403675740487476</v>
       </c>
       <c r="J83" t="n">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="K83" t="n">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="84">
@@ -43466,7 +43873,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.0005984715956173465</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -43481,7 +43888,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>-0.2177191328934967</v>
       </c>
       <c r="J84" t="n">
         <v>955</v>
@@ -43493,23 +43900,23 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22539</v>
+        <v>21735</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.03699102829537612</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
-        <v>2677</v>
+        <v>2490</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -43518,19 +43925,19 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.0751004016064257</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>1421</v>
+        <v>955</v>
       </c>
       <c r="K85" t="n">
-        <v>11</v>
+        <v>460</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -43540,10 +43947,10 @@
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0</v>
+        <v>0.03699102829537612</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>2677</v>
@@ -43555,32 +43962,32 @@
         <v>0</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0</v>
+        <v>0.0751004016064257</v>
       </c>
       <c r="J86" t="n">
-        <v>1435</v>
+        <v>1421</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>22807</v>
+        <v>22539</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.01189050090953458</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>2677</v>
@@ -43595,7 +44002,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -43604,23 +44011,23 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>23921</v>
+        <v>22807</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.04884465295742535</v>
+        <v>0.01189050090953458</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
-        <v>49090</v>
+        <v>2677</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -43629,10 +44036,10 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>17.33769144564812</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1455</v>
+        <v>1443</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -43641,35 +44048,35 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>25642</v>
+        <v>23921</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.07194515279461561</v>
+        <v>0.04884465295742535</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>49120</v>
+        <v>49090</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>2979</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0612955795477694</v>
+        <v>17.33769144564812</v>
       </c>
       <c r="J89" t="n">
-        <v>1478</v>
+        <v>1455</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -43678,60 +44085,60 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>21722</v>
+        <v>25642</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.1528741907807503</v>
+        <v>0.07194515279461561</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>3183</v>
+        <v>49120</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>2979</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.9389047774429452</v>
+        <v>0.0612955795477694</v>
       </c>
       <c r="J90" t="n">
-        <v>958</v>
+        <v>1478</v>
       </c>
       <c r="K90" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>21735</v>
+        <v>21722</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.0005984715956173465</v>
+        <v>-0.1528741907807503</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>2490</v>
+        <v>3183</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -43740,35 +44147,35 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>-0.2177191328934967</v>
+        <v>-0.9389047774429452</v>
       </c>
       <c r="J91" t="n">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="K91" t="n">
-        <v>461</v>
+        <v>451</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>22539</v>
+        <v>21735</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.03699102829537612</v>
+        <v>0.0005984715956173465</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
-        <v>2677</v>
+        <v>2490</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -43777,19 +44184,19 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.0751004016064257</v>
+        <v>-0.2177191328934967</v>
       </c>
       <c r="J92" t="n">
-        <v>1421</v>
+        <v>955</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>461</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -43799,10 +44206,10 @@
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0</v>
+        <v>0.03699102829537612</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>2677</v>
@@ -43814,35 +44221,35 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0</v>
+        <v>0.0751004016064257</v>
       </c>
       <c r="J93" t="n">
-        <v>1435</v>
+        <v>1421</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22807</v>
+        <v>22539</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.01189050090953458</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
-        <v>49090</v>
+        <v>2677</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -43851,32 +44258,32 @@
         <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>17.33769144564812</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>1442</v>
+        <v>1435</v>
       </c>
       <c r="K94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>23921</v>
+        <v>22807</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.04884465295742535</v>
+        <v>0.01189050090953458</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>49090</v>
@@ -43888,71 +44295,108 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0</v>
+        <v>17.33769144564812</v>
       </c>
       <c r="J95" t="n">
-        <v>1453</v>
+        <v>1442</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>23921</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.04884465295742535</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>49090</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1453</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>25642</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.07194515279461561</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>49124</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>4253</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>0.08732939498879609</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>1486</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>3920</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>45941</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>4253</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>528</v>
       </c>
     </row>
@@ -43968,7 +44412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -46684,7 +47128,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>32739</v>
@@ -47004,60 +47448,60 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>49946</v>
+        <v>65789</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.2051118821020467</v>
+        <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4380</v>
+        <v>32739</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>-0.3632795464457043</v>
+        <v>3.801715365605466</v>
       </c>
       <c r="J82" t="n">
-        <v>2823</v>
+        <v>3796</v>
       </c>
       <c r="K82" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>50832</v>
+        <v>49946</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0.01773915829095423</v>
+        <v>-0.2408153338704039</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>6765</v>
+        <v>4380</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -47066,13 +47510,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.5445205479452054</v>
+        <v>-0.8673972934516061</v>
       </c>
       <c r="J83" t="n">
-        <v>2821</v>
+        <v>2823</v>
       </c>
       <c r="K83" t="n">
-        <v>826</v>
+        <v>785</v>
       </c>
     </row>
     <row r="84">
@@ -47088,7 +47532,7 @@
         <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>0.01773915829095423</v>
       </c>
       <c r="E84" t="n">
         <v>24</v>
@@ -47103,7 +47547,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0</v>
+        <v>0.5445205479452054</v>
       </c>
       <c r="J84" t="n">
         <v>2821</v>
@@ -47115,20 +47559,20 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>51527</v>
+        <v>50832</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.01367248977022348</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>6765</v>
@@ -47143,29 +47587,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>3269</v>
+        <v>2821</v>
       </c>
       <c r="K85" t="n">
-        <v>345</v>
+        <v>826</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>54037</v>
+        <v>51527</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.04871232557688202</v>
+        <v>0.01367248977022348</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>6765</v>
@@ -47180,29 +47624,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>3642</v>
+        <v>3269</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>57513</v>
+        <v>54037</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.06432629494605548</v>
+        <v>0.04871232557688202</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>6765</v>
@@ -47217,7 +47661,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>3666</v>
+        <v>3642</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -47226,20 +47670,20 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>60496</v>
+        <v>57513</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0.05186653452262967</v>
+        <v>0.06432629494605548</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>6765</v>
@@ -47254,7 +47698,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3711</v>
+        <v>3666</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -47263,23 +47707,23 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>62834</v>
+        <v>60496</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>0.03864718328484528</v>
+        <v>0.05186653452262967</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
-        <v>6879</v>
+        <v>6765</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -47288,10 +47732,10 @@
         <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01685144124168515</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>3751</v>
+        <v>3711</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -47300,23 +47744,23 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>49946</v>
+        <v>62834</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.2051118821020467</v>
+        <v>0.03864718328484528</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
-        <v>4380</v>
+        <v>6879</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -47325,35 +47769,35 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>-0.3632795464457043</v>
+        <v>0.01685144124168515</v>
       </c>
       <c r="J90" t="n">
-        <v>2823</v>
+        <v>3751</v>
       </c>
       <c r="K90" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>50832</v>
+        <v>49946</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0.01773915829095423</v>
+        <v>-0.2051118821020467</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>6765</v>
+        <v>4380</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -47362,32 +47806,32 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.5445205479452054</v>
+        <v>-0.3632795464457043</v>
       </c>
       <c r="J91" t="n">
-        <v>2821</v>
+        <v>2823</v>
       </c>
       <c r="K91" t="n">
-        <v>826</v>
+        <v>785</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>51527</v>
+        <v>50832</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.01367248977022348</v>
+        <v>0.01773915829095423</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>6765</v>
@@ -47399,32 +47843,32 @@
         <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5445205479452054</v>
       </c>
       <c r="J92" t="n">
-        <v>3656</v>
+        <v>2821</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>826</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>54037</v>
+        <v>51527</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.04871232557688202</v>
+        <v>0.01367248977022348</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>6765</v>
@@ -47439,29 +47883,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>3642</v>
+        <v>3656</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>57513</v>
+        <v>54037</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.06432629494605548</v>
+        <v>0.04871232557688202</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>6765</v>
@@ -47476,7 +47920,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>3669</v>
+        <v>3642</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -47485,23 +47929,23 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>60637</v>
+        <v>57513</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0.05431815415645159</v>
+        <v>0.06432629494605548</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
-        <v>57180</v>
+        <v>6765</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -47510,10 +47954,10 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>7.452328159645233</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>3715</v>
+        <v>3669</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -47522,59 +47966,96 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>12/2024</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>60637</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.05431815415645159</v>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>57180</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>7.452328159645233</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3715</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>12/2025</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B97" t="n">
         <v>62834</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="3" t="n">
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
         <v>0.03623200356218151</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F97" t="n">
         <v>6750</v>
       </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
         <v>130</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I97" s="3" t="n">
         <v>-0.8796782091640434</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J97" t="n">
         <v>3756</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>12888</v>
       </c>
-      <c r="F97" s="4" t="n">
+      <c r="F98" s="4" t="n">
         <v>2370</v>
       </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="J97" s="4" t="n">
+      <c r="J98" s="4" t="n">
         <v>933</v>
       </c>
     </row>
@@ -47590,7 +48071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -50306,7 +50787,7 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -50626,7 +51107,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -50639,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -50654,16 +51135,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K82" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -50676,7 +51157,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -50694,7 +51175,7 @@
         <v>220</v>
       </c>
       <c r="K83" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84">
@@ -50737,7 +51218,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -50750,7 +51231,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -50765,16 +51246,16 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -50787,7 +51268,7 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -50802,16 +51283,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -50824,7 +51305,7 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -50848,7 +51329,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -50861,7 +51342,7 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -50876,7 +51357,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -50885,7 +51366,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -50898,7 +51379,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -50913,7 +51394,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -50922,7 +51403,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -50935,7 +51416,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -50950,16 +51431,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K90" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -50972,7 +51453,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -50990,13 +51471,13 @@
         <v>220</v>
       </c>
       <c r="K91" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -51009,7 +51490,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -51024,16 +51505,16 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>133</v>
+        <v>220</v>
       </c>
       <c r="K92" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -51046,7 +51527,7 @@
         <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -51061,16 +51542,16 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -51083,7 +51564,7 @@
         <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -51107,7 +51588,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -51120,7 +51601,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -51135,7 +51616,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -51144,7 +51625,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -51157,46 +51638,83 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>233</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>4319</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>238</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -51212,7 +51730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -53928,7 +54446,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -54248,20 +54766,20 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/2019</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7159</v>
+        <v>7101</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>-0.02823401656033664</v>
+        <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54276,16 +54794,16 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>218</v>
+        <v>456</v>
       </c>
       <c r="K82" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/2020</t>
+          <t>11/2019</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -54295,10 +54813,10 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>0</v>
+        <v>0.008167863681171665</v>
       </c>
       <c r="E83" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -54313,10 +54831,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="K83" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="84">
@@ -54359,7 +54877,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>11/2021</t>
+          <t>11/2020</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -54372,7 +54890,7 @@
         <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -54387,29 +54905,29 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>425</v>
+        <v>190</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>11/2022</t>
+          <t>11/2021</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>7342</v>
+        <v>7159</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>0.02556222936164269</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -54424,29 +54942,29 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>11/2023</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7367</v>
+        <v>7342</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.00340506673930809</v>
+        <v>0.02556222936164269</v>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -54461,7 +54979,7 @@
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -54470,7 +54988,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>11/2024</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -54480,10 +54998,10 @@
         <v>0</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.00340506673930809</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -54498,7 +55016,7 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -54507,7 +55025,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>11/2025</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -54520,7 +55038,7 @@
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -54535,7 +55053,7 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -54544,20 +55062,20 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>12/2019</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>7159</v>
+        <v>7367</v>
       </c>
       <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-0.02823401656033664</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -54572,16 +55090,16 @@
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>218</v>
+        <v>453</v>
       </c>
       <c r="K90" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>12/2020</t>
+          <t>12/2019</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -54591,10 +55109,10 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.02823401656033664</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -54609,16 +55127,16 @@
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>190</v>
+        <v>218</v>
       </c>
       <c r="K91" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/2021</t>
+          <t>12/2020</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -54631,7 +55149,7 @@
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -54646,29 +55164,29 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>425</v>
+        <v>190</v>
       </c>
       <c r="K92" t="n">
-        <v>15</v>
+        <v>249</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/2022</t>
+          <t>12/2021</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>7342</v>
+        <v>7159</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>0.02556222936164269</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
@@ -54683,29 +55201,29 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>7367</v>
+        <v>7342</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>0.00340506673930809</v>
+        <v>0.02556222936164269</v>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
@@ -54720,7 +55238,7 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -54729,7 +55247,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>12/2024</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -54739,10 +55257,10 @@
         <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>0</v>
+        <v>0.00340506673930809</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -54757,7 +55275,7 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -54766,7 +55284,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>12/2025</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -54779,46 +55297,83 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
+        <v>15</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>449</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>12/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>7367</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
         <v>9</v>
       </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
         <v>453</v>
       </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Saldo = </t>
         </is>
       </c>
-      <c r="B97" s="4" t="n">
+      <c r="B98" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="F97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="4" t="n">
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4" t="n">
         <v>263</v>
       </c>
     </row>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11801,7 +11801,7 @@
         <v>11108</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
@@ -36502,7 +36502,7 @@
         <v>7353</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -40161,7 +40161,7 @@
         <v>17597</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -8139,10 +8139,10 @@
         <v>0.0002660193529079241</v>
       </c>
       <c r="J82" t="n">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -36499,10 +36499,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7353</v>
+        <v>7360</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17597</v>
+        <v>17601</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11798,10 +11798,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11108</v>
+        <v>11118</v>
       </c>
       <c r="K82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>2232</v>
@@ -22775,10 +22775,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -36499,10 +36499,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7360</v>
+        <v>7361</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -40143,7 +40143,7 @@
         <v>0.05128060573995854</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17601</v>
+        <v>17603</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11801,7 +11801,7 @@
         <v>11118</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -22778,7 +22778,7 @@
         <v>6461</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -40134,13 +40134,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>242419</v>
+        <v>242488</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.05128060573995854</v>
+        <v>0.05157983295315576</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -40161,7 +40161,7 @@
         <v>17603</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -40177,7 +40177,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.04578023999768995</v>
+        <v>-0.04605176338622942</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -40134,13 +40134,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>242488</v>
+        <v>242709</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.05157983295315576</v>
+        <v>0.05253822736064252</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
@@ -40161,7 +40161,7 @@
         <v>17603</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -40177,7 +40177,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.04605176338622942</v>
+        <v>-0.04692038614142863</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -47479,7 +47479,7 @@
         <v>3796</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -8142,7 +8142,7 @@
         <v>2671</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -11801,7 +11801,7 @@
         <v>11118</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -40161,7 +40161,7 @@
         <v>17603</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -43820,7 +43820,7 @@
         <v>1502</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4483,7 +4483,7 @@
         <v>2260</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -40161,7 +40161,7 @@
         <v>17603</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -47479,7 +47479,7 @@
         <v>3796</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -8142,7 +8142,7 @@
         <v>2671</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -43820,7 +43820,7 @@
         <v>1502</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4480,10 +4480,10 @@
         <v>2.565813106173346e-05</v>
       </c>
       <c r="J82" t="n">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -8139,10 +8139,10 @@
         <v>0.0002660193529079241</v>
       </c>
       <c r="J82" t="n">
-        <v>2671</v>
+        <v>2673</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -11798,10 +11798,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11118</v>
+        <v>11125</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -22763,22 +22763,22 @@
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>2232</v>
+        <v>5378</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>34967</v>
+        <v>34977</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>6461</v>
+        <v>6463</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -26434,7 +26434,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -36499,10 +36499,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7361</v>
+        <v>7363</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17603</v>
+        <v>17606</v>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -43817,10 +43817,10 @@
         <v>0.02453022130943012</v>
       </c>
       <c r="J82" t="n">
-        <v>1502</v>
+        <v>1505</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -47476,10 +47476,10 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J82" t="n">
-        <v>3796</v>
+        <v>3800</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -8139,10 +8139,10 @@
         <v>0.0002660193529079241</v>
       </c>
       <c r="J82" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11801,7 +11801,7 @@
         <v>11125</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,10 +22760,10 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
-        <v>5378</v>
+        <v>5452</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -36502,7 +36502,7 @@
         <v>7363</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -40143,7 +40143,7 @@
         <v>0.05253822736064252</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11801,7 +11801,7 @@
         <v>11125</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -36502,7 +36502,7 @@
         <v>7363</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>5452</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05253822736064252</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -47479,7 +47479,7 @@
         <v>3800</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11801,7 +11801,7 @@
         <v>11125</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -40161,7 +40161,7 @@
         <v>17606</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11801,7 +11801,7 @@
         <v>11125</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -40161,7 +40161,7 @@
         <v>17606</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>5452</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05253822736064252</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40161,7 +40161,7 @@
         <v>17606</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11798,10 +11798,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11125</v>
+        <v>11130</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>5452</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -36499,10 +36499,10 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7363</v>
+        <v>7368</v>
       </c>
       <c r="K82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -40134,16 +40134,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>242709</v>
+        <v>242699</v>
       </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>0.05253822736064252</v>
+        <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17606</v>
+        <v>17613</v>
       </c>
       <c r="K82" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -40177,7 +40177,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>-0.04692038614142863</v>
+        <v>-0.04688111611502314</v>
       </c>
       <c r="E83" t="n">
         <v>10</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -47476,10 +47476,10 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J82" t="n">
-        <v>3800</v>
+        <v>3801</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11798,7 +11798,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11130</v>
+        <v>11129</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>5452</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17613</v>
+        <v>17620</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -47476,7 +47476,7 @@
         <v>3.801715365605466</v>
       </c>
       <c r="J82" t="n">
-        <v>3801</v>
+        <v>3800</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>5452</v>
@@ -22775,7 +22775,7 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -36499,7 +36499,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7368</v>
+        <v>7369</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40161,7 +40161,7 @@
         <v>17620</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11798,10 +11798,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11129</v>
+        <v>11131</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,16 +22760,16 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
-        <v>5452</v>
+        <v>6867</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>34977</v>
+        <v>61290</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -36499,7 +36499,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7369</v>
+        <v>7371</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40158,7 +40158,7 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17620</v>
+        <v>17622</v>
       </c>
       <c r="K82" t="n">
         <v>2</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -11801,7 +11801,7 @@
         <v>11131</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>6867</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11798,10 +11798,10 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11131</v>
+        <v>11133</v>
       </c>
       <c r="K82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>6867</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -40158,10 +40158,10 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17622</v>
+        <v>17623</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>38509</v>
@@ -8124,7 +8124,7 @@
         <v>0.001115782342744426</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>30019</v>
@@ -11783,7 +11783,7 @@
         <v>0.01632673853657915</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>50256</v>
@@ -15442,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -19101,7 +19101,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -22760,7 +22760,7 @@
         <v>0.02383614434902586</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>6867</v>
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -30091,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -32973,7 +32973,7 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -36484,7 +36484,7 @@
         <v>0.0703305572880361</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>58530</v>
@@ -40143,7 +40143,7 @@
         <v>0.05249486109786031</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>39864</v>
@@ -43802,7 +43802,7 @@
         <v>0.02988191822636356</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>49124</v>
@@ -47461,7 +47461,7 @@
         <v>0.04702867874080911</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>32739</v>
@@ -51120,7 +51120,7 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -54779,7 +54779,7 @@
         <v>-0.03610696348581512</v>
       </c>
       <c r="E82" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>

--- a/regionais/registroCXM.xlsx
+++ b/regionais/registroCXM.xlsx
@@ -11798,7 +11798,7 @@
         <v>0.0008402879896109848</v>
       </c>
       <c r="J82" t="n">
-        <v>11133</v>
+        <v>11132</v>
       </c>
       <c r="K82" t="n">
         <v>1</v>
@@ -36499,7 +36499,7 @@
         <v>0.002300587741393787</v>
       </c>
       <c r="J82" t="n">
-        <v>7371</v>
+        <v>7370</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -40158,7 +40158,7 @@
         <v>0.1641831151065077</v>
       </c>
       <c r="J82" t="n">
-        <v>17623</v>
+        <v>17622</v>
       </c>
       <c r="K82" t="n">
         <v>1</v>
